--- a/verification/cases/roundtrip/formatting/init.xlsx
+++ b/verification/cases/roundtrip/formatting/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{461FDF52-3BEA-4714-A943-BD8D1FC86B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="15" windowWidth="15135" windowHeight="8130"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,18 +63,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="yy/mm/dd"/>
-    <numFmt numFmtId="168" formatCode="d/m/yy;@"/>
-    <numFmt numFmtId="169" formatCode="dd\-mm\-yy"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="&quot;£&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="yy/mm/dd"/>
+    <numFmt numFmtId="167" formatCode="d/m/yy;@"/>
+    <numFmt numFmtId="168" formatCode="dd\-mm\-yy"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="&quot;£&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +115,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -116,20 +123,27 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -167,7 +181,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -201,6 +215,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -235,9 +250,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,20 +426,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -431,7 +447,7 @@
         <v>39045</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -439,7 +455,7 @@
         <v>39045</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -447,7 +463,7 @@
         <v>39045</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -455,7 +471,7 @@
         <v>39045</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -463,7 +479,7 @@
         <v>39045</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -471,15 +487,15 @@
         <v>39045</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="7"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -487,7 +503,7 @@
         <v>10.52</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -495,7 +511,7 @@
         <v>10.52</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -503,7 +519,7 @@
         <v>10.52</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -518,18 +534,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
